--- a/Result/profitability/4942.xlsx
+++ b/Result/profitability/4942.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM68"/>
+  <dimension ref="A1:AM69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>3.57</v>
       </c>
       <c r="M2" t="n">
-        <v>1.0975</v>
+        <v>1.07625</v>
       </c>
       <c r="N2" t="n">
-        <v>22.91375</v>
+        <v>22.2975</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>3.75</v>
       </c>
       <c r="M3" t="n">
-        <v>1.5125</v>
+        <v>1.39375</v>
       </c>
       <c r="N3" t="n">
-        <v>23.01875</v>
+        <v>22.6</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.31</v>
       </c>
       <c r="M4" t="n">
-        <v>1.525</v>
+        <v>1.48125</v>
       </c>
       <c r="N4" t="n">
-        <v>22.92375</v>
+        <v>22.37125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>2.41</v>
       </c>
       <c r="M5" t="n">
-        <v>1.75</v>
+        <v>1.74375</v>
       </c>
       <c r="N5" t="n">
-        <v>22.775</v>
+        <v>22.13375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.43</v>
       </c>
       <c r="M6" t="n">
-        <v>1.89</v>
+        <v>1.8175</v>
       </c>
       <c r="N6" t="n">
-        <v>22.59</v>
+        <v>22.05125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,16 +1264,16 @@
         <v>0.87</v>
       </c>
       <c r="M7" t="n">
-        <v>1.89375</v>
+        <v>1.765</v>
       </c>
       <c r="N7" t="n">
-        <v>22.2125</v>
+        <v>21.295</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -9064,6 +9064,133 @@
       </c>
       <c r="AM68" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>4942</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1364</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1118</v>
+      </c>
+      <c r="E69" t="n">
+        <v>247</v>
+      </c>
+      <c r="F69" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="G69" t="n">
+        <v>49</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>3.58%</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J69" t="n">
+        <v>44</v>
+      </c>
+      <c r="K69" t="n">
+        <v>36</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.68375</v>
+      </c>
+      <c r="N69" t="n">
+        <v>21.9675</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
+      </c>
+      <c r="V69" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W69" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="X69" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>-1.699999999999999</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>-0.08598887202832572</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>-0.04999999999999999</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>-0.1612903225806451</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>-5.129999999999999</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>-0.2211206896551724</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK69" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
